--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.66 ± 0.06</t>
+          <t>0.63 ± 0.06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.06</t>
+          <t>0.52 ± 0.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71 ± 0.19</t>
+          <t>0.71 ± 0.16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.49 ± 0.26</t>
+          <t>0.39 ± 0.18</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,12 +498,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.68 ± 0.15</t>
+          <t>0.73 ± 0.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.62 ± 0.32</t>
+          <t>0.45 ± 0.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
